--- a/측정일지_업로드양식.xlsx
+++ b/측정일지_업로드양식.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\cursor\측정일지_Html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACA9DC8-B246-415A-9539-CC611BE63510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157808C0-EF2A-4668-A791-E1DBD11593BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="측정일지_업로드(25년 자료)" sheetId="8" r:id="rId1"/>
@@ -54154,13 +54154,13 @@
         <v>0</v>
       </c>
       <c r="AH366" s="1">
-        <v>0</v>
+        <v>5600000</v>
       </c>
       <c r="AI366" s="24">
-        <v>46002</v>
+        <v>46034</v>
       </c>
       <c r="AJ366" s="1">
-        <v>0</v>
+        <v>5600000</v>
       </c>
       <c r="AK366" s="24" t="s">
         <v>1265</v>
